--- a/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LCID_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>LCID</t>
   </si>
@@ -656,283 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>405300</v>
+      </c>
+      <c r="E8" s="3">
         <v>282500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>522700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>336600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>259400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>235000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>234500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>172700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>157200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>137800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>150900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>149400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>257700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>195500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>97300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>57700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26400</v>
-      </c>
-      <c r="V8" s="3">
-        <v>200</v>
       </c>
       <c r="W8" s="3">
         <v>200</v>
       </c>
       <c r="X8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3600</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>594200</v>
+        <v>841600</v>
       </c>
       <c r="E9" s="3">
+        <v>647200</v>
+      </c>
+      <c r="F9" s="3">
         <v>944600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>670200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>531800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>463600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>443200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>412500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>470400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>404800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>410000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>469700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>555800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>615300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>492500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>292300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>246000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>151500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3300</v>
       </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
       <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
         <v>100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2500</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,80 +951,83 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-311700</v>
+        <v>-436200</v>
       </c>
       <c r="E10" s="3">
+        <v>-364700</v>
+      </c>
+      <c r="F10" s="3">
         <v>-421900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-333600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-272400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-228500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-208800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-212500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-269800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-232100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-252900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-331900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-404900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-351100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-357600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-297000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-195000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-188300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-125100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W10" s="3">
-        <v>200</v>
       </c>
       <c r="X10" s="3">
         <v>200</v>
       </c>
       <c r="Y10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1100</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,8 +1040,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1063,80 +1075,81 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>321300</v>
+      </c>
+      <c r="E12" s="3">
         <v>335700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>361000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>325300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>273800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>251200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>280300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>324400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>287200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>284600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>243000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>230800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>233500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>229800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>221300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>213800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>186100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>163600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>242400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>176800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>167400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>169500</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1149,8 +1162,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1235,71 +1251,74 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>48200</v>
+        <v>23600</v>
       </c>
       <c r="E14" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F14" s="3">
         <v>1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-120300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>13500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>29600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>19900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-6000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>22500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,59 +1334,62 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E15" s="3">
         <v>116400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>122100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>120100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>111100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>98000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>90800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>69500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>66200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>68800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>55400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>49800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1407,8 +1429,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1436,85 +1461,86 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1234000</v>
+        <v>1463300</v>
       </c>
       <c r="E17" s="3">
+        <v>1287000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1587500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1278600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1062500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>927000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>967400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>970500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>967800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>902700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>894000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>890200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>987000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>899100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1007500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>883000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>656500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>655200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>512100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>500000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>249100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>299100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>203300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
+      <c r="AB17" s="3">
+        <v>0</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
@@ -1522,80 +1548,83 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-951600</v>
+        <v>-1058000</v>
       </c>
       <c r="E18" s="3">
+        <v>-1004600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1064800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-942000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-803000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-691900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-733000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-770500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-767200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-729900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-736900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-752400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-836200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-749700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-749800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-687500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-559200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-597500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-485700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-499800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-248900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-298800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-199700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1608,8 +1637,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1640,80 +1672,81 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-262900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>46800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-120400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-297500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-293700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>254200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-105500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-26200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-59600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-41200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>40100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>285000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>158400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>339000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>516700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-559900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-24500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-449100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-111400</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1726,80 +1759,83 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-835600</v>
+        <v>-849800</v>
       </c>
       <c r="E21" s="3">
+        <v>-888600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-679700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-868700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-571600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-296400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-348400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-955100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-595500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-635000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-643200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-632000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-739600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-740000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-409500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-478400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-177800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-42600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1009200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-509400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-254800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-743000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-306400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1812,58 +1848,61 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E22" s="3">
         <v>41100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
-      </c>
-      <c r="S22" s="3">
-        <v>100</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
@@ -1881,10 +1920,10 @@
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1898,85 +1937,88 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1033800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1028200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-812300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-978800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-541800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-367500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-396600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-992000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-643500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-680700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-653800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-630600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-763600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-779400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-472800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-530000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-220400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-81000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1045700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-524400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-261700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-747900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-311200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
+      <c r="AB23" s="3">
+        <v>0</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
@@ -1984,65 +2026,68 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>100</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
       <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2053,16 +2098,16 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
+      <c r="AB24" s="3">
+        <v>0</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
@@ -2070,8 +2115,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2156,85 +2204,88 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1034900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1028300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-814000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-978400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-539400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-366200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-397200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-992500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-643400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-680900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-653800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-630900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-764200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-779500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-472600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-530100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-220400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-81300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1045700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-524400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-261700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-748000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-311300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
+      <c r="AB26" s="3">
+        <v>0</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
@@ -2242,85 +2293,88 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1259300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1134300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1176800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1034500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-739300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-731100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-636900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-949600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-790300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-684800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-653800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-630900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-764200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-779500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1726900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-530100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-220400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-81300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1045700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-524400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-261700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-297500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
+      <c r="AB27" s="3">
+        <v>0</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
@@ -2328,8 +2382,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2414,8 +2471,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2500,8 +2560,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2586,8 +2649,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2672,80 +2738,83 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>262900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-46800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>120400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>297500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>293700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-254200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>105500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>26200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>59600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>41200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-40100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-285000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-158400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-339000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-516700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>559900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>24500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>449100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>111400</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,85 +2827,88 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1034900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1028300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-814000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-978400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-539400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-366200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-397200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-992500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-643400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-680900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-653800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-630900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-764200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-779500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1726900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-530100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-220400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-81300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1045700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-524400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-261700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-297500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
+      <c r="AB33" s="3">
+        <v>0</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
@@ -2844,8 +2916,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2930,85 +3005,88 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1034900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1028300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-814000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-978400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-539400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-366200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-397200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-992500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-643400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-680900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-653800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-630900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-764200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-779500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1726900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-530100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-220400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-81300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1045700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-524400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-261700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-297500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
+      <c r="AB35" s="3">
+        <v>0</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
@@ -3016,99 +3094,105 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3139,8 +3223,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3171,153 +3256,157 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>732600</v>
+      </c>
+      <c r="E41" s="3">
         <v>700400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>997800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1635100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1795700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1854900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1606900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1893600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1353600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2169500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1369900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1164400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2775300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1735800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1264100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3157400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5391800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6262900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4796900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>557900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>810000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3">
         <v>4200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>28700</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>631100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>701900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1030100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1756000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2424100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1578300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1862800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1824900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2489800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3258200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2474000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2078400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2177200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2078000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1136600</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3">
         <v>500</v>
@@ -3325,8 +3414,8 @@
       <c r="X42" s="3">
         <v>500</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
+      <c r="Y42" s="3">
+        <v>500</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
@@ -3337,83 +3426,86 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E43" s="3">
         <v>131200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>190300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>155000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>148000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>114600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>109600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>138600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>62900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>27700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>27900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>600</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,83 +3515,86 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1378700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1468900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1109500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>981100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>713300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>471400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>407800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>506800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>509900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>565700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>696200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>799000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>849800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1017600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>834400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>685300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>553000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>333900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>127300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>61200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>28200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6300</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3509,89 +3604,92 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>304300</v>
+      </c>
+      <c r="E45" s="3">
         <v>353800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>291500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>264800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>174800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>250600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>96400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>90200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>63200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>67000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>55800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>145100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>126300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>118100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>137800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>113700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>67900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3601,148 +3699,154 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2776500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2756700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3299700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3800100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3951100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4423300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4873900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4247000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4001500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4834000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4757200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5391500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6256900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4119800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4912000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4156400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4966500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5864400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6507000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4986800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>682400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>868600</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3">
         <v>5300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E47" s="3">
         <v>13600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>512200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>687700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>807800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>947200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1050100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>601200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>739100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>688400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>542600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>479700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>288100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>441700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>530000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>513700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>278100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3758,12 +3862,12 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="3">
         <v>2070200</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,77 +3877,80 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4471900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4287200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4220100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3980100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3804100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3553100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3474500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3442700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3278600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3189300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3032400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2894700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2698500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2536100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2381900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2166200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1813600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1494200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1344100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1109700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1014400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>899900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3853,14 +3960,17 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3945,8 +4055,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4031,8 +4144,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4117,94 +4233,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>436200</v>
+      </c>
+      <c r="E52" s="3">
         <v>425700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>355000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>355200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>306100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>294500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>249400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>198300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>204000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>185400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>180600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>175300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>171600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>163300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>55300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>51500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>71200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>42700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>39300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>31300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4289,94 +4411,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7698800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7483200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8387000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8823000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8869100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9218000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9647900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8489200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8223300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8897000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8512700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8941200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9415100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7260900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7879200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6887800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7129400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7401800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7881700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6139200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1736100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1799800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3">
         <v>2075500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4407,8 +4535,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4439,85 +4568,86 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>366900</v>
+      </c>
+      <c r="E57" s="3">
         <v>484900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>487500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>393000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>213700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>121300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>139200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>113600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>108700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>104600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>140100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>145700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>229100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>79800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>129100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>66400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>41300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9200</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
+      <c r="AB57" s="3">
+        <v>0</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
@@ -4525,335 +4655,347 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>779400</v>
+      </c>
+      <c r="E58" s="3">
         <v>782300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>820100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>450600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>292200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>242500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>168800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>88400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>105600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>110300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>109200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>86400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>35600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>20200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>25500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>19500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>10800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2500</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB58" s="3">
         <v>300</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>798100</v>
+      </c>
+      <c r="E59" s="3">
         <v>818700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>796400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>791200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>610500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>556800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>527100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>649400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>527100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>596100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>569400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>639700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>498000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>444800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>688300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>719800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>517900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>436600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>335300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>232600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>175000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>247300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3">
         <v>100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2438200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2694300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2636100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2105000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1534000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1331500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1165300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1146100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1010900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1036700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1008400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1037900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>885600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1015000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>937600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>825100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>654100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>511900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>396100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>269400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>199800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>259100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>0</v>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="3">
         <v>400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2877300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2385800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2376600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2363000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2448700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2315700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2308100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2315900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2310400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2313100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2318700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2319500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2324100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2311500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2073200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2069900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1994600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1994100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1992900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4200</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4869,83 +5011,86 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>420300</v>
+      </c>
+      <c r="E62" s="3">
         <v>250200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>258700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>519200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>609000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>889200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1171400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>624800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>702700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>226100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>177800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>245600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>302600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>518800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>761500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>770400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1066300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1583400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1019900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>164800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1309500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3">
         <v>72500</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4955,8 +5100,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5041,8 +5189,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5127,8 +5278,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5213,94 +5367,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5850500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5445100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5386200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5101900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4596900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4369500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4475300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4745300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4056100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4160400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3661000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3535200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3455200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3629100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3529500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3656600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3419000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3572400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3972400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1294000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>368500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1572800</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3">
         <v>72500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>400</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5331,8 +5491,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5417,8 +5578,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5503,41 +5667,44 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2906300</v>
+      </c>
+      <c r="E70" s="3">
         <v>2389500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>2283500</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1920700</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1864600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1664800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1299800</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>1060200</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>651300</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>504500</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -5566,14 +5733,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>5836800</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>4454800</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5589,8 +5756,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5675,85 +5845,88 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17673900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-16639100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15610700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14796700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13818300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13278900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12912700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12515500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11523000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10879600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10198800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9545000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8914100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8149900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7370300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6897700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6367600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6147200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6065900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5020200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4495800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4234100</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-200</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
+      <c r="AB72" s="3">
+        <v>0</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
@@ -5761,8 +5934,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5847,8 +6023,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5933,8 +6112,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6019,85 +6201,88 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1058000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-351400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>717300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1800400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2407600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3183700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3872800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2683700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3515900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4232200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4851700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5406000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5959800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3631900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4349700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3231200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3710400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3829500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3909400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4845200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-4469200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-4227900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3">
         <v>2003000</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
+      <c r="AB76" s="3">
+        <v>0</v>
       </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
@@ -6105,8 +6290,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6191,176 +6379,182 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1034900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1028300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-814000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-978400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-539400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-366200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-397200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-992500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-643400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-680900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-653800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-630900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-764200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-779500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1726900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-530100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-220400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-81300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1045700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-524400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-261700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2915300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-297500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
+      <c r="AB81" s="3">
+        <v>0</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
@@ -6368,8 +6562,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6400,85 +6597,86 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E83" s="3">
         <v>98000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>90800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>66200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>68800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>67500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>55400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>50700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>38200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>50700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>42400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>38200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>36300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4800</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6486,8 +6684,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6572,8 +6773,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6658,8 +6862,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6744,8 +6951,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6830,8 +7040,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6916,85 +7129,88 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1222200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1185700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-916400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-756700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-830200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-428600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-533100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-462800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-507000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-516700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-474500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-513600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-801300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-648500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-569500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-513600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-494600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-312700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-291600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-235100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-218700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-192800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
@@ -7002,8 +7218,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7034,85 +7253,86 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-253800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-253200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-325400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-198800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-182700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-161200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-291600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-159700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-234300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-198200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-272600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-192500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-203700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-241800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-289900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-290100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-309800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-185100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-121900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-92800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-111800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-94800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7120,8 +7340,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7206,8 +7429,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7292,80 +7518,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-282300</v>
+      </c>
+      <c r="E94" s="3">
         <v>875200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-84700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>255100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>694000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>614000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1584400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>283700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-311300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>317500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>652200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1132400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-438000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-392700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1729000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-185100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-121400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-92800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-111700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-94800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7378,8 +7607,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7410,8 +7642,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7454,8 +7687,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7496,8 +7729,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7582,8 +7818,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7668,8 +7907,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7754,94 +7996,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1545800</v>
+      </c>
+      <c r="E100" s="3">
         <v>35300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>369600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>376100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>78900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>62700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1831000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>719100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>997200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>28000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>35100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3013600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1512800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>17600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-187300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1899600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4624700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>101000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>511100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>398000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2075400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7884,8 +8132,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7926,90 +8174,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-275200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-631500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-125500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-57300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>248100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-286600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>540100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-815900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>798000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>205600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1610900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1875300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-835700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>471600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1926700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2238600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-867000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1465500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4240400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-245800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>197600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>101500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
